--- a/notebooks/results/Q3_reduced_scotland_tot=4_flex=0.1.xlsx
+++ b/notebooks/results/Q3_reduced_scotland_tot=4_flex=0.1.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marta/Documents/MSc CAM/Dissertation/PyPSA-GB/notebooks/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDCE08B-C232-8440-BBF7-910EFE78A4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61693386-1593-8642-948B-7A6475417785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13780" yWindow="660" windowWidth="16460" windowHeight="17400" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17400" activeTab="3" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Inflexible" sheetId="4" r:id="rId1"/>
     <sheet name="Temporal" sheetId="2" r:id="rId2"/>
     <sheet name="Spatial" sheetId="1" r:id="rId3"/>
     <sheet name="Both" sheetId="3" r:id="rId4"/>
+    <sheet name="CFE" sheetId="5" r:id="rId5"/>
+    <sheet name="CFE + both" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Both!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">CFE!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CFE + both'!$A$1:$N$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inflexible!$A$1:$N$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Spatial!$A$1:$N$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Temporal!$A$1:$N$37</definedName>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="63">
   <si>
     <t>Optimal Capacity</t>
   </si>
@@ -230,22 +234,13 @@
     <t>Hydrogen Gas</t>
   </si>
   <si>
-    <t xml:space="preserve">Optimal objective 4.78840493e+07 </t>
+    <t>Data Centre Cost:</t>
   </si>
   <si>
-    <t>INFO:gurobipy:Optimal objective 4.78840493e+07</t>
+    <t xml:space="preserve">Optimal objective 8.187527603e+07 </t>
   </si>
   <si>
-    <t xml:space="preserve">Optimal objective 4.81281538e+07 </t>
-  </si>
-  <si>
-    <t>INFO:gurobipy:Optimal objective 4.81281538e+07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimal objective 4.81906149e+07 </t>
-  </si>
-  <si>
-    <t>INFO:gurobipy:Optimal objective 4.81906149e+07</t>
+    <t>INFO:gurobipy:Optimal objective 8.187527603e+07</t>
   </si>
 </sst>
 </file>
@@ -366,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -392,11 +387,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4972E32-7E17-D640-8808-61170EE7E9D2}">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
@@ -826,7 +833,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
@@ -868,7 +875,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
@@ -910,7 +917,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -952,7 +959,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
@@ -994,7 +1001,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1036,7 +1043,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
@@ -1078,7 +1085,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
@@ -1120,7 +1127,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,7 +1169,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1204,7 +1211,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,7 +1253,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="1" t="s">
         <v>53</v>
       </c>
@@ -1288,7 +1295,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1330,7 +1337,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1372,7 +1379,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
@@ -1414,7 +1421,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="A17" s="11"/>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1456,7 +1463,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
@@ -1498,7 +1505,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1540,7 +1547,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
@@ -1582,7 +1589,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1712,7 +1719,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
@@ -1754,7 +1761,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
+      <c r="A25" s="12"/>
       <c r="B25" s="1" t="s">
         <v>56</v>
       </c>
@@ -1840,7 +1847,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
+      <c r="A27" s="12"/>
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
@@ -1926,7 +1933,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
+      <c r="A29" s="11"/>
       <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1968,7 +1975,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
@@ -2010,7 +2017,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
+      <c r="A31" s="12"/>
       <c r="B31" s="1" t="s">
         <v>39</v>
       </c>
@@ -2169,14 +2176,13 @@
         <v>9787781</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>65</v>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="2">
+        <f>-$M$26</f>
+        <v>14118940</v>
       </c>
     </row>
   </sheetData>
@@ -2193,7 +2199,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4BF803-EC4E-F842-B68E-528EC71F1DE9}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.1640625" customWidth="1"/>
@@ -2296,7 +2302,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2338,7 +2344,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2380,7 +2386,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -2422,7 +2428,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
@@ -2464,7 +2470,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -2506,7 +2512,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
@@ -2548,7 +2554,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
@@ -2590,7 +2596,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2632,7 +2638,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2674,7 +2680,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
@@ -2716,7 +2722,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="1" t="s">
         <v>53</v>
       </c>
@@ -2758,7 +2764,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
@@ -2800,7 +2806,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
@@ -2842,7 +2848,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
@@ -2884,7 +2890,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="A17" s="11"/>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,7 +2932,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
@@ -2968,7 +2974,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -3010,7 +3016,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
@@ -3052,7 +3058,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3182,7 +3188,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="1" t="s">
         <v>40</v>
       </c>
@@ -3224,7 +3230,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="1" t="s">
         <v>55</v>
       </c>
@@ -3266,7 +3272,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
+      <c r="A26" s="12"/>
       <c r="B26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3352,7 +3358,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28" s="12"/>
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
@@ -3438,7 +3444,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="1" t="s">
         <v>57</v>
       </c>
@@ -3480,7 +3486,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="1" t="s">
         <v>58</v>
       </c>
@@ -3522,7 +3528,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
+      <c r="A32" s="12"/>
       <c r="B32" s="1" t="s">
         <v>39</v>
       </c>
@@ -3608,7 +3614,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
+      <c r="A34" s="12"/>
       <c r="B34" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,6 +3727,15 @@
       <c r="C41" s="2">
         <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
         <v>9535869</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="2">
+        <f>-$M$27</f>
+        <v>14097900</v>
       </c>
     </row>
   </sheetData>
@@ -3738,7 +3753,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274D0A62-B14B-AA4E-B6C1-C6D101FC58CC}">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -3831,7 +3846,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
@@ -3873,7 +3888,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
@@ -3915,7 +3930,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -3957,7 +3972,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
@@ -3999,7 +4014,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -4041,7 +4056,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
@@ -4083,7 +4098,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
@@ -4125,7 +4140,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -4167,7 +4182,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4209,7 +4224,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
@@ -4251,7 +4266,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="1" t="s">
         <v>53</v>
       </c>
@@ -4293,7 +4308,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4335,7 +4350,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4377,7 +4392,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4419,7 +4434,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="A17" s="11"/>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4461,7 +4476,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4503,7 +4518,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4545,7 +4560,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4587,7 +4602,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4717,7 +4732,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
@@ -4759,7 +4774,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="1" t="s">
         <v>56</v>
       </c>
@@ -4801,7 +4816,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
+      <c r="A26" s="12"/>
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
@@ -4887,7 +4902,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28" s="12"/>
       <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4973,7 +4988,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="1" t="s">
         <v>57</v>
       </c>
@@ -5015,7 +5030,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="1" t="s">
         <v>58</v>
       </c>
@@ -5057,7 +5072,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
+      <c r="A32" s="12"/>
       <c r="B32" s="1" t="s">
         <v>39</v>
       </c>
@@ -5217,14 +5232,13 @@
         <v>9994974</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>63</v>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="2">
+        <f>-$M$27</f>
+        <v>14124690</v>
       </c>
     </row>
   </sheetData>
@@ -5242,7 +5256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4D27E0-A6E7-0A4E-A9C8-EA69BF34BB6E}">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -5334,7 +5348,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
@@ -5376,7 +5390,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
@@ -5418,7 +5432,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -5460,7 +5474,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
@@ -5502,7 +5516,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
@@ -5544,7 +5558,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="1" t="s">
         <v>51</v>
       </c>
@@ -5586,7 +5600,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
@@ -5628,7 +5642,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
@@ -5670,7 +5684,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
@@ -5712,7 +5726,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,7 +5768,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="1" t="s">
         <v>53</v>
       </c>
@@ -5796,7 +5810,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
@@ -5838,7 +5852,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
@@ -5880,7 +5894,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
@@ -5922,7 +5936,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="A17" s="11"/>
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -5964,7 +5978,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
@@ -6006,7 +6020,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="1" t="s">
         <v>27</v>
       </c>
@@ -6048,7 +6062,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
@@ -6090,7 +6104,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -6220,7 +6234,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="1" t="s">
         <v>40</v>
       </c>
@@ -6262,7 +6276,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="1" t="s">
         <v>55</v>
       </c>
@@ -6304,7 +6318,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
+      <c r="A26" s="11"/>
       <c r="B26" s="1" t="s">
         <v>56</v>
       </c>
@@ -6346,7 +6360,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
+      <c r="A27" s="12"/>
       <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
@@ -6432,7 +6446,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
+      <c r="A29" s="12"/>
       <c r="B29" s="1" t="s">
         <v>36</v>
       </c>
@@ -6518,7 +6532,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="1" t="s">
         <v>57</v>
       </c>
@@ -6560,7 +6574,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
+      <c r="A32" s="11"/>
       <c r="B32" s="1" t="s">
         <v>58</v>
       </c>
@@ -6602,7 +6616,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
+      <c r="A33" s="12"/>
       <c r="B33" s="1" t="s">
         <v>39</v>
       </c>
@@ -6688,7 +6702,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
+      <c r="A35" s="12"/>
       <c r="B35" s="1" t="s">
         <v>59</v>
       </c>
@@ -6801,14 +6815,23 @@
         <v>9985787</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C42" s="2">
+        <f>-$M$28</f>
+        <v>14080300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -6822,4 +6845,3051 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBEC364B-95F3-6542-9C15-C4F497796E61}">
+  <dimension ref="A1:N39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4">
+        <v>372.43929000000003</v>
+      </c>
+      <c r="D2" s="4">
+        <v>372.43929000000003</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>813779.8</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="11"/>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1642.8915400000001</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1642.8915400000001</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3589718</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="11"/>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4">
+        <v>9185.8067100000007</v>
+      </c>
+      <c r="D4" s="4">
+        <v>9185.8067100000007</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20070990</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.2">
+      <c r="A5" s="11"/>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
+        <v>23586</v>
+      </c>
+      <c r="D5" s="4">
+        <v>23586</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>51535410</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="11"/>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3534.0360000000001</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3534.0360000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>7721869</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4">
+        <v>13695</v>
+      </c>
+      <c r="D7" s="4">
+        <v>13695</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3567759</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3567759</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.119229</v>
+      </c>
+      <c r="J7" s="3">
+        <v>26355820</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>40697210</v>
+      </c>
+      <c r="M7" s="3">
+        <v>40697210</v>
+      </c>
+      <c r="N7" s="4">
+        <v>11.406941</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4067.2939999999999</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4067.2939999999999</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8887037</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="4">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4643.509</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4643.509</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.19319800000000001</v>
+      </c>
+      <c r="J9" s="3">
+        <v>19391.490000000002</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>57858.12</v>
+      </c>
+      <c r="M9" s="3">
+        <v>99256.85</v>
+      </c>
+      <c r="N9" s="4">
+        <v>21.375356</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="11"/>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="4">
+        <v>834.51107000000002</v>
+      </c>
+      <c r="D10" s="4">
+        <v>834.51107000000002</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1327.7829999999999</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1327.7829999999999</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>7.2800000000000002E-4</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1822079</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>71700.3</v>
+      </c>
+      <c r="M10" s="3">
+        <v>71876.929999999993</v>
+      </c>
+      <c r="N10" s="4">
+        <v>54.133128999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="11"/>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1897.296</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1897.296</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1410729</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1410729</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.34029599999999999</v>
+      </c>
+      <c r="J11" s="3">
+        <v>247507.3</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9471836</v>
+      </c>
+      <c r="N11" s="4">
+        <v>6.7141409999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="11"/>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4">
+        <v>48629.190949999997</v>
+      </c>
+      <c r="D12" s="4">
+        <v>48629.190949999997</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>52178340</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+      <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4">
+        <v>254.358</v>
+      </c>
+      <c r="D13" s="4">
+        <v>254.358</v>
+      </c>
+      <c r="E13" s="3">
+        <v>238897.2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>238897.2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.42984699999999998</v>
+      </c>
+      <c r="J13" s="3">
+        <v>34872.370000000003</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>2000389</v>
+      </c>
+      <c r="N13" s="4">
+        <v>8.3734300000000008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="11"/>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="4">
+        <v>4570</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4570</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4061245</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4061245</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.40671600000000002</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5924205</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>40612450</v>
+      </c>
+      <c r="M14" s="3">
+        <v>68046630</v>
+      </c>
+      <c r="N14" s="4">
+        <v>16.755116999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="11"/>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="4">
+        <v>53544.201999999997</v>
+      </c>
+      <c r="D15" s="4">
+        <v>53544.201999999997</v>
+      </c>
+      <c r="E15" s="3">
+        <v>25483100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>25483100</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.21781500000000001</v>
+      </c>
+      <c r="J15" s="3">
+        <v>6631744</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>102405100</v>
+      </c>
+      <c r="N15" s="4">
+        <v>4.0185490000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="11"/>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4">
+        <v>78.5</v>
+      </c>
+      <c r="D16" s="4">
+        <v>78.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>171522.5</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4">
+        <v>27270.741000000002</v>
+      </c>
+      <c r="D17" s="4">
+        <v>27270.741000000002</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11319050</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11319050</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.18995999999999999</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3016082</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>42150350</v>
+      </c>
+      <c r="N17" s="4">
+        <v>3.7238410000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="11"/>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3662.89</v>
+      </c>
+      <c r="D18" s="4">
+        <v>3662.89</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>8003415</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="11"/>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="4">
+        <v>55.819389999999999</v>
+      </c>
+      <c r="D19" s="4">
+        <v>55.819389999999999</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>121965.4</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="4">
+        <v>40470.421999999999</v>
+      </c>
+      <c r="D20" s="4">
+        <v>40470.421999999999</v>
+      </c>
+      <c r="E20" s="3">
+        <v>13150640</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>13150640</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.14871599999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1414899</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>90278670</v>
+      </c>
+      <c r="N20" s="4">
+        <v>6.8649630000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A21" s="12"/>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="4">
+        <v>4643.1779999999999</v>
+      </c>
+      <c r="D21" s="4">
+        <v>4643.1779999999999</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>10145340</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="4">
+        <v>230800</v>
+      </c>
+      <c r="D22" s="4">
+        <v>230800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>35388420</v>
+      </c>
+      <c r="F22" s="3">
+        <v>21320510</v>
+      </c>
+      <c r="G22" s="3">
+        <v>14067910</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-14067910</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.112451</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>134043700</v>
+      </c>
+      <c r="N22" s="4">
+        <v>2.3637139999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4">
+        <v>12450</v>
+      </c>
+      <c r="D23" s="4">
+        <v>12450</v>
+      </c>
+      <c r="E23" s="3">
+        <v>9520578</v>
+      </c>
+      <c r="F23" s="3">
+        <v>5861339</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3659240</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3659240</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.56544399999999995</v>
+      </c>
+      <c r="J23" s="3">
+        <v>30862490</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>70784100</v>
+      </c>
+      <c r="N23" s="4">
+        <v>4.6017739999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3653.0947500000002</v>
+      </c>
+      <c r="D24" s="4">
+        <v>3653.0947500000002</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>136057.4</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-136057.4</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1.7045000000000001E-2</v>
+      </c>
+      <c r="J24" s="3">
+        <v>7845955</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A25" s="12"/>
+      <c r="B25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="4">
+        <v>278.38099999999997</v>
+      </c>
+      <c r="D25" s="4">
+        <v>278.38099999999997</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>87212.04</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-87212.04</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.14337900000000001</v>
+      </c>
+      <c r="J25" s="3">
+        <v>521050.4</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>436060.2</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1877543</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-1877543</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-14118940</v>
+      </c>
+      <c r="N26" s="4">
+        <v>-7.5199040000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="12"/>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>52178340</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-52178340</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-411891500</v>
+      </c>
+      <c r="N27" s="4">
+        <v>-7.8939170000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="4">
+        <v>26471.973000000002</v>
+      </c>
+      <c r="D28" s="4">
+        <v>26471.973000000002</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2577047</v>
+      </c>
+      <c r="F28" s="3">
+        <v>5998543</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-3421497</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0.148261</v>
+      </c>
+      <c r="J28" s="3">
+        <v>61262760</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>16741690</v>
+      </c>
+      <c r="N28" s="4">
+        <v>1.9522489999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="45" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="4">
+        <v>857.70799999999997</v>
+      </c>
+      <c r="D29" s="4">
+        <v>857.70799999999997</v>
+      </c>
+      <c r="E29" s="3">
+        <v>137415</v>
+      </c>
+      <c r="F29" s="3">
+        <v>269283.90000000002</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-131868.9</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0.21701100000000001</v>
+      </c>
+      <c r="J29" s="3">
+        <v>2005961</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>548921.5</v>
+      </c>
+      <c r="N29" s="4">
+        <v>1.3496999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="45" x14ac:dyDescent="0.2">
+      <c r="A30" s="11"/>
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="4">
+        <v>457.99400000000003</v>
+      </c>
+      <c r="D30" s="4">
+        <v>457.99400000000003</v>
+      </c>
+      <c r="E30" s="3">
+        <v>31335.279999999999</v>
+      </c>
+      <c r="F30" s="3">
+        <v>253138.2</v>
+      </c>
+      <c r="G30" s="3">
+        <v>-221803</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.28427000000000002</v>
+      </c>
+      <c r="J30" s="3">
+        <v>1222520</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>549749.4</v>
+      </c>
+      <c r="N30" s="4">
+        <v>1.932515</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="60" x14ac:dyDescent="0.2">
+      <c r="A31" s="12"/>
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5300</v>
+      </c>
+      <c r="D31" s="4">
+        <v>5300</v>
+      </c>
+      <c r="E31" s="3">
+        <v>830462.2</v>
+      </c>
+      <c r="F31" s="3">
+        <v>2235843</v>
+      </c>
+      <c r="G31" s="3">
+        <v>-1405381</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.26478200000000002</v>
+      </c>
+      <c r="J31" s="3">
+        <v>12985880</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>10545950</v>
+      </c>
+      <c r="N31" s="4">
+        <v>3.4393009999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="4">
+        <v>46768.008000000002</v>
+      </c>
+      <c r="D32" s="4">
+        <v>46768.008000000002</v>
+      </c>
+      <c r="E32" s="3">
+        <v>85847.27</v>
+      </c>
+      <c r="F32" s="3">
+        <v>93875.38</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-8028.1059999999998</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.78561999999999999</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="I33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="7" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="2">
+        <f>SUM(L1:L30)</f>
+        <v>81875278.61999999</v>
+      </c>
+      <c r="M33" s="2">
+        <f>SUM(M1:M30)</f>
+        <v>151879039.67999998</v>
+      </c>
+      <c r="N33" s="2">
+        <f>SUM(N1:N30)</f>
+        <v>130.15159799999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="I34" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J34" s="2">
+        <f>SUM(J12,J14)</f>
+        <v>58102545</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="2">
+        <f>SUM(J17)</f>
+        <v>3016082</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="2">
+        <f>SUMIFS($D$2:$D$32,$B$2:$B$32, "Solar PV")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>121341.18438999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Solar PV")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>11184690.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
+        <v>9647826</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="2">
+        <f>-$M$26</f>
+        <v>14118940</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N32" xr:uid="{EBEC364B-95F3-6542-9C15-C4F497796E61}"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A92586-5AA0-4346-8AF7-C6AB4137DC20}">
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
+        <v>372.4393</v>
+      </c>
+      <c r="D2" s="3">
+        <v>372.4393</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>813779.8</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="11"/>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1642.8920000000001</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1642.8920000000001</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>3589718</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="11"/>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3">
+        <v>9185.8070000000007</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9185.8070000000007</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20070990</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11"/>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3">
+        <v>23586</v>
+      </c>
+      <c r="D5" s="3">
+        <v>23586</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>51535410</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="11"/>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3534.0360000000001</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3534.0360000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>7721869</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3">
+        <v>13695</v>
+      </c>
+      <c r="D7" s="3">
+        <v>13695</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3501002</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3501002</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.11699809999999999</v>
+      </c>
+      <c r="J7" s="3">
+        <v>26422570</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>39740210</v>
+      </c>
+      <c r="M7" s="3">
+        <v>39740210</v>
+      </c>
+      <c r="N7" s="4">
+        <v>11.351096999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4067.2939999999999</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4067.2939999999999</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8887037</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4564.6790000000001</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4564.6790000000001</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.18991820000000001</v>
+      </c>
+      <c r="J9" s="3">
+        <v>19470.32</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>56875.9</v>
+      </c>
+      <c r="M9" s="3">
+        <v>97186.44</v>
+      </c>
+      <c r="N9" s="4">
+        <v>21.290948</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="11"/>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3">
+        <v>834.51110000000006</v>
+      </c>
+      <c r="D10" s="3">
+        <v>834.51110000000006</v>
+      </c>
+      <c r="E10" s="3">
+        <v>37.805959999999999</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>37.805959999999999</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2.0730700000000001E-5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1823369</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>2041.5219999999999</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2152.4699999999998</v>
+      </c>
+      <c r="N10" s="4">
+        <v>56.942774999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="11"/>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1897.296</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1897.296</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1392269</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1392269</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.33584320000000001</v>
+      </c>
+      <c r="J11" s="3">
+        <v>265967.7</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9282304</v>
+      </c>
+      <c r="N11" s="4">
+        <v>6.667033</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11"/>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>48629.19</v>
+      </c>
+      <c r="D12" s="3">
+        <v>48629.19</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>52178340</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+      <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="3">
+        <v>254.358</v>
+      </c>
+      <c r="D13" s="3">
+        <v>254.358</v>
+      </c>
+      <c r="E13" s="3">
+        <v>237958.9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>237958.9</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.42815910000000001</v>
+      </c>
+      <c r="J13" s="3">
+        <v>35810.61</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1973243</v>
+      </c>
+      <c r="N13" s="4">
+        <v>8.29237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="11"/>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4570</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4570</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4026833</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4026833</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.40327000000000002</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5958617</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>40268330</v>
+      </c>
+      <c r="M14" s="3">
+        <v>67154340</v>
+      </c>
+      <c r="N14" s="4">
+        <v>16.676715000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="11"/>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="3">
+        <v>53544.2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>53544.2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>25351440</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>25351440</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.21668989999999999</v>
+      </c>
+      <c r="J15" s="3">
+        <v>6763405</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>101261700</v>
+      </c>
+      <c r="N15" s="4">
+        <v>3.9943170000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="11"/>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3">
+        <v>78.5</v>
+      </c>
+      <c r="D16" s="3">
+        <v>78.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>171522.5</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="3">
+        <v>27270.74</v>
+      </c>
+      <c r="D17" s="3">
+        <v>27270.74</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11263220</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11263220</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.18902279999999999</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3071915</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>41619570</v>
+      </c>
+      <c r="N17" s="4">
+        <v>3.6951749999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="11"/>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3662.89</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3662.89</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>8003415</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="11"/>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="3">
+        <v>55.819389999999999</v>
+      </c>
+      <c r="D19" s="3">
+        <v>55.819389999999999</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>121965.4</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="3">
+        <v>40470.42</v>
+      </c>
+      <c r="D20" s="3">
+        <v>40470.42</v>
+      </c>
+      <c r="E20" s="3">
+        <v>13102590</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>13102590</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.14817269999999999</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1462947</v>
+      </c>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>89510120</v>
+      </c>
+      <c r="N20" s="4">
+        <v>6.8314810000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="12"/>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="3">
+        <v>4643.1779999999999</v>
+      </c>
+      <c r="D21" s="3">
+        <v>4643.1779999999999</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>10145340</v>
+      </c>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="3">
+        <v>230800</v>
+      </c>
+      <c r="D22" s="3">
+        <v>230800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>34843930</v>
+      </c>
+      <c r="F22" s="3">
+        <v>21634590</v>
+      </c>
+      <c r="G22" s="3">
+        <v>13209350</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-13209350</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.1119943</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>128749000</v>
+      </c>
+      <c r="N22" s="4">
+        <v>2.2796110000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="3">
+        <v>12450</v>
+      </c>
+      <c r="D23" s="3">
+        <v>12450</v>
+      </c>
+      <c r="E23" s="3">
+        <v>9512087</v>
+      </c>
+      <c r="F23" s="3">
+        <v>5921316</v>
+      </c>
+      <c r="G23" s="3">
+        <v>3590771</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3590771</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0.56733670000000003</v>
+      </c>
+      <c r="J23" s="3">
+        <v>30794020</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>69208700</v>
+      </c>
+      <c r="N23" s="4">
+        <v>4.4843450000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="3">
+        <v>26000000</v>
+      </c>
+      <c r="D24" s="3">
+        <v>26000000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>167658.1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-167658.1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2.9512070000000002E-6</v>
+      </c>
+      <c r="J24" s="3">
+        <v>56809830000</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1.67658</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-234283.6</v>
+      </c>
+      <c r="N24" s="4">
+        <v>-1.397389</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11"/>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="3">
+        <v>3653.0949999999998</v>
+      </c>
+      <c r="D25" s="3">
+        <v>3653.0949999999998</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>124699.8</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-124699.8</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1.562261E-2</v>
+      </c>
+      <c r="J25" s="3">
+        <v>7857312</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="11"/>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="3">
+        <v>278.38099999999997</v>
+      </c>
+      <c r="D26" s="3">
+        <v>278.38099999999997</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>83875.42</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-83875.42</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0.1378935</v>
+      </c>
+      <c r="J26" s="3">
+        <v>524387.1</v>
+      </c>
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>419377.1</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="12"/>
+      <c r="B27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="3">
+        <v>156000000</v>
+      </c>
+      <c r="D27" s="3">
+        <v>156000000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>16869.5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-16869.5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>16869.5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4.9490959999999997E-8</v>
+      </c>
+      <c r="J27" s="3">
+        <v>340860000000</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0.16869000000000001</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-33157.050000000003</v>
+      </c>
+      <c r="N27" s="4">
+        <v>-1.9655039999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1877543</v>
+      </c>
+      <c r="G28" s="3">
+        <v>-1877543</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>-13965940</v>
+      </c>
+      <c r="N28" s="4">
+        <v>-7.4384139999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="12"/>
+      <c r="B29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>52178340</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-52178340</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>-407915500</v>
+      </c>
+      <c r="N29" s="4">
+        <v>-7.817717</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="3">
+        <v>26471.97</v>
+      </c>
+      <c r="D30" s="3">
+        <v>26471.97</v>
+      </c>
+      <c r="E30" s="3">
+        <v>3505123</v>
+      </c>
+      <c r="F30" s="3">
+        <v>6722566</v>
+      </c>
+      <c r="G30" s="3">
+        <v>-3217443</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0.17682339999999999</v>
+      </c>
+      <c r="J30" s="3">
+        <v>61058700</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>16559150</v>
+      </c>
+      <c r="N30" s="4">
+        <v>1.619051</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="11"/>
+      <c r="B31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="3">
+        <v>857.70799999999997</v>
+      </c>
+      <c r="D31" s="3">
+        <v>857.70799999999997</v>
+      </c>
+      <c r="E31" s="3">
+        <v>180467.20000000001</v>
+      </c>
+      <c r="F31" s="3">
+        <v>300479.3</v>
+      </c>
+      <c r="G31" s="3">
+        <v>-120012.1</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0.2566291</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1994104</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>543364.6</v>
+      </c>
+      <c r="N31" s="4">
+        <v>1.1297820000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="11"/>
+      <c r="B32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="3">
+        <v>457.99400000000003</v>
+      </c>
+      <c r="D32" s="3">
+        <v>457.99400000000003</v>
+      </c>
+      <c r="E32" s="3">
+        <v>32953.08</v>
+      </c>
+      <c r="F32" s="3">
+        <v>243302.8</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-210349.7</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0.27605800000000003</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1211067</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>543975.69999999995</v>
+      </c>
+      <c r="N32" s="4">
+        <v>1.969101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A33" s="12"/>
+      <c r="B33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1033753</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2316997</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1283245</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.28934409999999999</v>
+      </c>
+      <c r="J33" s="3">
+        <v>12863740</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>10310820</v>
+      </c>
+      <c r="N33" s="4">
+        <v>3.077169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="3">
+        <v>13000000</v>
+      </c>
+      <c r="D34" s="3">
+        <v>13000000</v>
+      </c>
+      <c r="E34" s="3">
+        <v>83829.03</v>
+      </c>
+      <c r="F34" s="3">
+        <v>83829.03</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.99909400000000004</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="12"/>
+      <c r="B35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="3">
+        <v>46768.01</v>
+      </c>
+      <c r="D35" s="3">
+        <v>46768.01</v>
+      </c>
+      <c r="E35" s="3">
+        <v>82921.179999999993</v>
+      </c>
+      <c r="F35" s="3">
+        <v>86335.64</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-3414.4650000000001</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.33413530000000002</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="14"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="I37" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J37" s="7" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37" s="2">
+        <f>SUM(L1:L30)</f>
+        <v>80486836.367269978</v>
+      </c>
+      <c r="M37" s="2">
+        <f>SUM(M1:M30)</f>
+        <v>143008795.25999999</v>
+      </c>
+      <c r="N37" s="2">
+        <f>SUM(N1:N30)</f>
+        <v>125.50589399999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="I38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="2">
+        <f>SUM(J12,J14)</f>
+        <v>58136957</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="2">
+        <f>SUM(J17)</f>
+        <v>3071915</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="2">
+        <f>SUMIFS($D$2:$D$32,$B$2:$B$32, "Solar PV")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($D$2:$D$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>121341.17939</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Solar PV")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Sewage Gas")</f>
+        <v>11420232.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="2">
+        <f>SUMIFS($J$2:$J$32,$B$2:$B$32, "Offshore Wind")+SUMIFS($J$2:$J$32,$B$2:$B$32, "Onshore Wind")</f>
+        <v>9835320</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="2">
+        <f>-$M$28</f>
+        <v>13965940</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N32" xr:uid="{EBEC364B-95F3-6542-9C15-C4F497796E61}"/>
+  <mergeCells count="5">
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>